--- a/data/trans_orig/P6607-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6607-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2012</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2012 (tasa de respuesta: 99,14%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>22886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40827</t>
+          <t>40662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59648</t>
+          <t>59086</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75050</t>
+          <t>74368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86923</t>
+          <t>86038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113729</t>
+          <t>112785</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,09%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>21592</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28857</t>
+          <t>28834</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>14448</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31490</t>
+          <t>31620</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36880</t>
+          <t>37451</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13867</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32582</t>
+          <t>31575</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8860</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36469</t>
+          <t>37242</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131494</t>
+          <t>133757</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172764</t>
+          <t>173654</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>180057</t>
+          <t>178762</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>210636</t>
+          <t>209652</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>321140</t>
+          <t>322001</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>373938</t>
+          <t>376590</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,98%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60001</t>
+          <t>59583</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92031</t>
+          <t>92270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35800</t>
+          <t>35310</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62529</t>
+          <t>61411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103083</t>
+          <t>102388</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>144760</t>
+          <t>146016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62784</t>
+          <t>60156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94542</t>
+          <t>93304</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>28233</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74296</t>
+          <t>74380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111303</t>
+          <t>115368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62344</t>
+          <t>63076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97049</t>
+          <t>95623</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28336</t>
+          <t>28205</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>78905</t>
+          <t>77620</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>115348</t>
+          <t>118245</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>150947</t>
+          <t>154557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>192761</t>
+          <t>194123</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192485</t>
+          <t>191758</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>223489</t>
+          <t>224214</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>353604</t>
+          <t>354096</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>408404</t>
+          <t>405980</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82559</t>
+          <t>81704</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>118753</t>
+          <t>117818</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37280</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63846</t>
+          <t>62407</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>128402</t>
+          <t>127633</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>172076</t>
+          <t>172751</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62481</t>
+          <t>63785</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94262</t>
+          <t>97544</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8770</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23696</t>
+          <t>23569</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75434</t>
+          <t>77607</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112112</t>
+          <t>112601</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59111</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91742</t>
+          <t>91299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7167</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23038</t>
+          <t>22265</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>69693</t>
+          <t>71195</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>107315</t>
+          <t>108735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>134187</t>
+          <t>135746</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>175429</t>
+          <t>174405</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>153937</t>
+          <t>155015</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>183633</t>
+          <t>182730</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>300960</t>
+          <t>299817</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>352754</t>
+          <t>349508</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67389</t>
+          <t>67655</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101063</t>
+          <t>103574</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20811</t>
+          <t>20208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42862</t>
+          <t>41903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92963</t>
+          <t>94281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134094</t>
+          <t>134766</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42220</t>
+          <t>40609</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72236</t>
+          <t>70358</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>20422</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49080</t>
+          <t>49615</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>82658</t>
+          <t>81348</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53024</t>
+          <t>52656</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84922</t>
+          <t>82000</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>6543</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65698</t>
+          <t>63741</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99989</t>
+          <t>99816</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51335</t>
+          <t>51343</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>75965</t>
+          <t>76162</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37740</t>
+          <t>37736</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54567</t>
+          <t>54329</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>95202</t>
+          <t>93842</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>126774</t>
+          <t>125498</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,28%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23048</t>
+          <t>23637</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44335</t>
+          <t>45129</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19380</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33161</t>
+          <t>33411</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57696</t>
+          <t>58349</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>19025</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38821</t>
+          <t>39137</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1079</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21765</t>
+          <t>23023</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44092</t>
+          <t>45160</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23848</t>
+          <t>23837</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45181</t>
+          <t>43376</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>29171</t>
+          <t>29055</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>53178</t>
+          <t>52497</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,12%</t>
         </is>
       </c>
     </row>
@@ -3916,97 +3916,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1546</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>539460</t>
+          <t>540046</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>613819</t>
+          <t>615807</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>661766</t>
+          <t>659481</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>718364</t>
+          <t>716899</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1214727</t>
+          <t>1216760</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1317617</t>
+          <t>1316405</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>266271</t>
+          <t>268030</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>332619</t>
+          <t>332366</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>130074</t>
+          <t>129340</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>176825</t>
+          <t>175282</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>410354</t>
+          <t>410417</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>489697</t>
+          <t>488004</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,69%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>231578</t>
+          <t>234360</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>291893</t>
+          <t>293645</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>37366</t>
+          <t>37145</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>68036</t>
+          <t>67265</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>279821</t>
+          <t>279964</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>347372</t>
+          <t>347201</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>246765</t>
+          <t>244837</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>304392</t>
+          <t>307204</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>40806</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>70279</t>
+          <t>69093</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>292255</t>
+          <t>289413</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>362058</t>
+          <t>360075</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2016</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2016 (tasa de respuesta: 99,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>16368</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>33448</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53088</t>
+          <t>52402</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71034</t>
+          <t>70993</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73575</t>
+          <t>73282</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99883</t>
+          <t>101667</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>59,47%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>20094</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39377</t>
+          <t>38650</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8838</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22817</t>
+          <t>23472</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33486</t>
+          <t>33120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56560</t>
+          <t>56778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3594</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>14631</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3951</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15720</t>
+          <t>15221</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>25256</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26653</t>
+          <t>26887</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2733</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>16238</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34471</t>
+          <t>34734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>103692</t>
+          <t>103138</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>139564</t>
+          <t>138103</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>174243</t>
+          <t>174549</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>203054</t>
+          <t>203159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>286351</t>
+          <t>284832</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>335816</t>
+          <t>335865</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,44%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71077</t>
+          <t>70916</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103605</t>
+          <t>101993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36523</t>
+          <t>36370</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61382</t>
+          <t>59372</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112614</t>
+          <t>114743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152339</t>
+          <t>156078</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51113</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80522</t>
+          <t>83382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>12255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28811</t>
+          <t>29307</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69532</t>
+          <t>69143</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104321</t>
+          <t>103553</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57035</t>
+          <t>54093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>86916</t>
+          <t>84612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>10436</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>25913</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71518</t>
+          <t>71160</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>108095</t>
+          <t>107207</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162123</t>
+          <t>161989</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>203522</t>
+          <t>204587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203293</t>
+          <t>202434</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>235194</t>
+          <t>233694</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>373899</t>
+          <t>377399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>429047</t>
+          <t>431113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,85%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86600</t>
+          <t>85298</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>123633</t>
+          <t>122189</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37206</t>
+          <t>37263</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64183</t>
+          <t>63086</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131482</t>
+          <t>130447</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>175759</t>
+          <t>175314</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64482</t>
+          <t>64151</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98123</t>
+          <t>97988</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16743</t>
+          <t>16734</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36718</t>
+          <t>35334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87660</t>
+          <t>87107</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125073</t>
+          <t>126412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74220</t>
+          <t>74992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108535</t>
+          <t>109317</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14330</t>
+          <t>14755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33801</t>
+          <t>34581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93565</t>
+          <t>92843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>133235</t>
+          <t>134399</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>130099</t>
+          <t>131114</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>168849</t>
+          <t>169953</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>150382</t>
+          <t>152083</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>181053</t>
+          <t>180976</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>291056</t>
+          <t>292848</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>346305</t>
+          <t>340250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>56,18%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>73338</t>
+          <t>72568</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>106645</t>
+          <t>108542</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45222</t>
+          <t>45394</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73343</t>
+          <t>71322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124819</t>
+          <t>126110</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>171125</t>
+          <t>170754</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41338</t>
+          <t>40804</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69766</t>
+          <t>69932</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>12068</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46495</t>
+          <t>46505</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>76330</t>
+          <t>76623</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55060</t>
+          <t>56425</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84237</t>
+          <t>86801</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20118</t>
+          <t>20187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65249</t>
+          <t>64311</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>100556</t>
+          <t>97679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51809</t>
+          <t>51155</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>78864</t>
+          <t>77439</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65696</t>
+          <t>66105</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85996</t>
+          <t>85246</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>122719</t>
+          <t>123349</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>158597</t>
+          <t>158842</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,72%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38950</t>
+          <t>39454</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64806</t>
+          <t>64173</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31947</t>
+          <t>31965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58767</t>
+          <t>58571</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90723</t>
+          <t>91240</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12810</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30012</t>
+          <t>30740</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12684</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16194</t>
+          <t>17085</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37408</t>
+          <t>38125</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19514</t>
+          <t>19295</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>40259</t>
+          <t>40337</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>19761</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>41290</t>
+          <t>40184</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -8512,62 +8512,62 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2287</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>5736</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>22,03%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>2287</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>6250</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>22,03%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>55,26%</t>
         </is>
       </c>
     </row>
@@ -8590,97 +8590,97 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8703,97 +8703,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8933,97 +8933,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
           <t>795</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -9046,97 +9046,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -9159,97 +9159,97 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -9272,97 +9272,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>506671</t>
+          <t>508040</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>584108</t>
+          <t>581427</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>689865</t>
+          <t>690314</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>746907</t>
+          <t>748661</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1214293</t>
+          <t>1216608</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1308733</t>
+          <t>1316116</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,78%</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>325486</t>
+          <t>328787</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>396758</t>
+          <t>395988</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>169017</t>
+          <t>168542</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>219304</t>
+          <t>219340</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>511582</t>
+          <t>516810</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>595566</t>
+          <t>599167</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,48%</t>
         </is>
       </c>
     </row>
@@ -9728,12 +9728,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>199267</t>
+          <t>201614</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>259207</t>
+          <t>259652</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>50812</t>
+          <t>49049</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>80108</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9778,12 +9778,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>259230</t>
+          <t>260269</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>324161</t>
+          <t>324340</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9813,7 +9813,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>247712</t>
+          <t>248389</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>311315</t>
+          <t>308930</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>45840</t>
+          <t>45228</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>75603</t>
+          <t>75326</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>302003</t>
+          <t>302411</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>369739</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9926,12 +9926,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10111,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2023</t>
+          <t>Población según la exposición a trabajos al aire libre en su trabajo en 2023 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10306,12 +10306,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2466</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10341,12 +10341,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17652</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32686</t>
+          <t>32948</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10376,12 +10376,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23324</t>
+          <t>22055</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>48055</t>
+          <t>47174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>58,91%</t>
         </is>
       </c>
     </row>
@@ -10419,12 +10419,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10454,12 +10454,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29784</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -10532,12 +10532,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18258</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10602,12 +10602,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>4902</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21893</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -10645,12 +10645,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24146</t>
+          <t>24113</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10660,12 +10660,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11612</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10715,12 +10715,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33139</t>
+          <t>32075</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -10875,12 +10875,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55356</t>
+          <t>57199</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89889</t>
+          <t>91432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10910,12 +10910,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96217</t>
+          <t>96665</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117508</t>
+          <t>117432</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10945,12 +10945,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>160381</t>
+          <t>160133</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>202516</t>
+          <t>200574</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10960,12 +10960,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -10988,12 +10988,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48361</t>
+          <t>47400</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34070</t>
+          <t>32618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11058,12 +11058,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42858</t>
+          <t>41944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73559</t>
+          <t>74298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -11101,12 +11101,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>21822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51508</t>
+          <t>50861</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11136,12 +11136,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>12052</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11151,12 +11151,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11171,12 +11171,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26708</t>
+          <t>25737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60758</t>
+          <t>57366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11186,12 +11186,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -11214,12 +11214,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22081</t>
+          <t>22036</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50064</t>
+          <t>48747</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12086</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11264,12 +11264,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27244</t>
+          <t>26595</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55669</t>
+          <t>55521</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11299,12 +11299,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -11444,12 +11444,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90030</t>
+          <t>89724</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121388</t>
+          <t>120179</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93414</t>
+          <t>93496</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>112233</t>
+          <t>113175</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11514,12 +11514,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190336</t>
+          <t>189469</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226405</t>
+          <t>228470</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11529,12 +11529,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -11557,12 +11557,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44600</t>
+          <t>43947</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72850</t>
+          <t>72533</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11592,12 +11592,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21721</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37640</t>
+          <t>37758</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11627,12 +11627,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>73231</t>
+          <t>73139</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>104810</t>
+          <t>104379</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11642,12 +11642,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -11670,12 +11670,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22344</t>
+          <t>21900</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43310</t>
+          <t>43070</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>19026</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11740,12 +11740,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>31829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55535</t>
+          <t>55390</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11755,12 +11755,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,08%</t>
         </is>
       </c>
     </row>
@@ -11783,12 +11783,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29700</t>
+          <t>29614</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>53721</t>
+          <t>54623</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22572</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11833,12 +11833,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11853,12 +11853,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42494</t>
+          <t>42771</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68341</t>
+          <t>69302</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11868,12 +11868,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>31813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>214886</t>
+          <t>215164</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>97560</t>
+          <t>94298</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>184395</t>
+          <t>185055</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112566</t>
+          <t>106228</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>410345</t>
+          <t>408012</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12098,12 +12098,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>54,88%</t>
         </is>
       </c>
     </row>
@@ -12126,12 +12126,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21668</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>153623</t>
+          <t>155802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32511</t>
+          <t>32087</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>131645</t>
+          <t>134629</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52757</t>
+          <t>53645</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>228006</t>
+          <t>239078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12211,12 +12211,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -12239,12 +12239,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>9402</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76116</t>
+          <t>75914</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12274,12 +12274,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>14262</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12309,12 +12309,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16000</t>
+          <t>16165</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71660</t>
+          <t>71241</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12324,12 +12324,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -12352,12 +12352,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77285</t>
+          <t>76775</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>437375</t>
+          <t>440439</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12387,12 +12387,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>18991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12422,12 +12422,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75515</t>
+          <t>74829</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>543002</t>
+          <t>571290</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12437,12 +12437,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>76,84%</t>
         </is>
       </c>
     </row>
@@ -12582,12 +12582,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56389</t>
+          <t>56393</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>79688</t>
+          <t>79698</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57768</t>
+          <t>57800</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>70031</t>
+          <t>70542</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>118015</t>
+          <t>118570</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>144672</t>
+          <t>146188</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12667,12 +12667,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -12695,12 +12695,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22516</t>
+          <t>22420</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40860</t>
+          <t>42267</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19560</t>
+          <t>19732</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36441</t>
+          <t>35063</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57395</t>
+          <t>56862</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,5%</t>
         </is>
       </c>
     </row>
@@ -12808,12 +12808,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15824</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>33244</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2468</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9398</t>
+          <t>9612</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19866</t>
+          <t>19962</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39579</t>
+          <t>39521</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12893,12 +12893,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -12921,12 +12921,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>39764</t>
+          <t>39349</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12956,12 +12956,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2942</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>26177</t>
+          <t>26681</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>45920</t>
+          <t>47281</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13006,12 +13006,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -13151,7 +13151,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -13201,7 +13201,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>10281</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>14496</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13236,12 +13236,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>66,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -13264,97 +13264,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1148</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3199</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>36,99%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>1148</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>3334</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>13,27%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>3975</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>38,56%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>1148</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>3444</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>7,62%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13412,62 +13412,62 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>2954</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>3414</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>4,41%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -13495,7 +13495,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>866</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13525,62 +13525,62 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>911</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>10,53%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>919</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -13720,97 +13720,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
           <t>1598</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="W34" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>1598</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -13833,97 +13833,97 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O35" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -13946,97 +13946,97 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="V36" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -14059,97 +14059,97 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
         </is>
       </c>
     </row>
@@ -14289,12 +14289,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>179497</t>
+          <t>208745</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>483755</t>
+          <t>483375</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -14304,12 +14304,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14324,12 +14324,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>393808</t>
+          <t>365120</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>498104</t>
+          <t>498252</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -14339,12 +14339,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14359,12 +14359,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>539710</t>
+          <t>552664</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>981182</t>
+          <t>990896</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -14374,12 +14374,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -14402,12 +14402,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>113441</t>
+          <t>113770</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>279186</t>
+          <t>279671</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14417,12 +14417,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>104829</t>
+          <t>101706</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>225167</t>
+          <t>245332</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14452,12 +14452,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>227840</t>
+          <t>224103</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>429608</t>
+          <t>439479</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14487,12 +14487,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -14515,12 +14515,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>63850</t>
+          <t>73875</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>178651</t>
+          <t>179885</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>24321</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>44164</t>
+          <t>45277</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -14565,12 +14565,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>103627</t>
+          <t>105177</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>207605</t>
+          <t>209816</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -14600,12 +14600,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -14628,12 +14628,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>193167</t>
+          <t>193105</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>741629</t>
+          <t>695128</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -14643,12 +14643,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>33124</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>55746</t>
+          <t>55349</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -14678,12 +14678,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>223928</t>
+          <t>221107</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>911621</t>
+          <t>918309</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -14713,12 +14713,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6607-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6607-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22886</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40662</t>
+          <t>41714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59086</t>
+          <t>59201</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74368</t>
+          <t>74713</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86038</t>
+          <t>85405</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>112785</t>
+          <t>112457</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>13662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21592</t>
+          <t>20072</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12246</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28834</t>
+          <t>28947</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>14122</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31620</t>
+          <t>30759</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17946</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37451</t>
+          <t>37175</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>14843</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31575</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>17009</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37242</t>
+          <t>38126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>133757</t>
+          <t>134578</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173654</t>
+          <t>172985</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178762</t>
+          <t>179239</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>209652</t>
+          <t>209523</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>322001</t>
+          <t>319007</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>376590</t>
+          <t>372797</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,41%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59583</t>
+          <t>62560</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92270</t>
+          <t>93093</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35310</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61411</t>
+          <t>61150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102388</t>
+          <t>104445</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146016</t>
+          <t>146317</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60156</t>
+          <t>61482</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93304</t>
+          <t>94068</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>9629</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28233</t>
+          <t>26684</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74380</t>
+          <t>76252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115368</t>
+          <t>113486</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63076</t>
+          <t>62189</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>95623</t>
+          <t>96843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>28205</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77620</t>
+          <t>79916</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>118245</t>
+          <t>118742</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154557</t>
+          <t>151742</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>194123</t>
+          <t>194591</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>191758</t>
+          <t>193757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>224214</t>
+          <t>224085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>354096</t>
+          <t>355757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>405980</t>
+          <t>410976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,87%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81704</t>
+          <t>80963</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>117818</t>
+          <t>117770</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>36592</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62407</t>
+          <t>63187</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>127633</t>
+          <t>126685</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>172751</t>
+          <t>172327</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63785</t>
+          <t>62595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97544</t>
+          <t>95235</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>23182</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>77607</t>
+          <t>76927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112601</t>
+          <t>113167</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>59468</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91299</t>
+          <t>91877</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22265</t>
+          <t>22339</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>71195</t>
+          <t>69433</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>108735</t>
+          <t>108377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>135746</t>
+          <t>135482</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>174405</t>
+          <t>175444</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>154544</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>182730</t>
+          <t>183232</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>299817</t>
+          <t>300707</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>349508</t>
+          <t>354027</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,62%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67655</t>
+          <t>67539</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103574</t>
+          <t>100555</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>20911</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41903</t>
+          <t>42221</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94281</t>
+          <t>93477</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134766</t>
+          <t>134825</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40609</t>
+          <t>41292</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70358</t>
+          <t>70860</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20422</t>
+          <t>19526</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49615</t>
+          <t>48004</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>81348</t>
+          <t>82311</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52656</t>
+          <t>53939</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>82000</t>
+          <t>85276</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22238</t>
+          <t>23427</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63741</t>
+          <t>63490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99816</t>
+          <t>97894</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3008,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51343</t>
+          <t>51168</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76162</t>
+          <t>75890</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37736</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54329</t>
+          <t>54576</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>93842</t>
+          <t>94057</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>125498</t>
+          <t>126011</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23637</t>
+          <t>24468</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45129</t>
+          <t>45574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19380</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t>33112</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58349</t>
+          <t>58552</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19025</t>
+          <t>18597</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>39137</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1096</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>9320</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>21981</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45160</t>
+          <t>43332</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23837</t>
+          <t>23429</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>43376</t>
+          <t>44995</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>12908</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>29055</t>
+          <t>28058</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>51817</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>83,64%</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>83,12%</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4872</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>68,83%</t>
         </is>
       </c>
     </row>
@@ -4715,12 +4715,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>540046</t>
+          <t>541129</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>615807</t>
+          <t>614118</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4750,12 +4750,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>659481</t>
+          <t>660305</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>716899</t>
+          <t>715033</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4765,12 +4765,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1216760</t>
+          <t>1216187</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1316405</t>
+          <t>1316115</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>55,8%</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4828,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>268030</t>
+          <t>266271</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>332366</t>
+          <t>333099</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,12 +4843,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>129340</t>
+          <t>129885</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>175282</t>
+          <t>174736</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4898,12 +4898,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>410417</t>
+          <t>408509</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>488004</t>
+          <t>489544</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -4941,12 +4941,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>234360</t>
+          <t>231893</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>293645</t>
+          <t>291650</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4956,12 +4956,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>37145</t>
+          <t>37633</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>67265</t>
+          <t>67307</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>279964</t>
+          <t>282063</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>347201</t>
+          <t>348803</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>244837</t>
+          <t>241382</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>307204</t>
+          <t>306903</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5069,12 +5069,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>40082</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>69093</t>
+          <t>70524</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>289413</t>
+          <t>294535</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>360075</t>
+          <t>360604</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,29%</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5519,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>15868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33448</t>
+          <t>32081</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52402</t>
+          <t>53089</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70993</t>
+          <t>70898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73282</t>
+          <t>73157</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101667</t>
+          <t>99131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5604,12 +5604,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -5632,12 +5632,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>21808</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38650</t>
+          <t>38492</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5647,12 +5647,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23472</t>
+          <t>22845</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5682,12 +5682,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33120</t>
+          <t>33031</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>57056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -5745,12 +5745,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>14643</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5760,12 +5760,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3579</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15221</t>
+          <t>15567</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5795,12 +5795,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>9627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>25048</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11352</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26887</t>
+          <t>26523</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>12566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5908,12 +5908,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16238</t>
+          <t>16077</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34734</t>
+          <t>34180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5943,12 +5943,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -6088,12 +6088,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>103138</t>
+          <t>102135</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>138103</t>
+          <t>140353</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>174549</t>
+          <t>175219</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>203159</t>
+          <t>203951</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>284832</t>
+          <t>285817</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>335865</t>
+          <t>334616</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -6201,12 +6201,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70916</t>
+          <t>69982</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101993</t>
+          <t>104993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36370</t>
+          <t>36647</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59372</t>
+          <t>60166</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114743</t>
+          <t>114598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156078</t>
+          <t>154283</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6286,12 +6286,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -6314,12 +6314,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>51144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>83382</t>
+          <t>82600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6329,12 +6329,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>12602</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29307</t>
+          <t>28907</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69143</t>
+          <t>70497</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103553</t>
+          <t>105562</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6399,12 +6399,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -6427,12 +6427,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>54093</t>
+          <t>56801</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84612</t>
+          <t>85188</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>25860</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6477,12 +6477,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71160</t>
+          <t>71283</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>107207</t>
+          <t>106036</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -6657,12 +6657,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>161989</t>
+          <t>161233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>204587</t>
+          <t>203823</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>202434</t>
+          <t>202134</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>233694</t>
+          <t>234017</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>377399</t>
+          <t>374918</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>431113</t>
+          <t>429818</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6742,12 +6742,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -6770,12 +6770,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>85298</t>
+          <t>86615</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>122189</t>
+          <t>122882</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37263</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>63086</t>
+          <t>62607</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>130447</t>
+          <t>132073</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>175314</t>
+          <t>176101</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -6883,12 +6883,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64151</t>
+          <t>65352</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97988</t>
+          <t>97909</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16734</t>
+          <t>16655</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35334</t>
+          <t>34752</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87107</t>
+          <t>86808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126412</t>
+          <t>124519</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -6996,12 +6996,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74992</t>
+          <t>73454</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109317</t>
+          <t>107753</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14755</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34581</t>
+          <t>33279</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92843</t>
+          <t>91472</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134399</t>
+          <t>132016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>131114</t>
+          <t>131760</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>169953</t>
+          <t>172986</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>152083</t>
+          <t>151899</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180976</t>
+          <t>182260</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>292848</t>
+          <t>293601</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>340250</t>
+          <t>344151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,82%</t>
         </is>
       </c>
     </row>
@@ -7339,12 +7339,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>72568</t>
+          <t>73237</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108542</t>
+          <t>107879</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45394</t>
+          <t>43432</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71322</t>
+          <t>71726</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126110</t>
+          <t>126808</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>170754</t>
+          <t>168931</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -7452,12 +7452,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40804</t>
+          <t>41927</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69932</t>
+          <t>69831</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7487,12 +7487,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12068</t>
+          <t>12174</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46505</t>
+          <t>47020</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>76623</t>
+          <t>76754</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -7565,12 +7565,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56425</t>
+          <t>53053</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86801</t>
+          <t>85183</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6245</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20187</t>
+          <t>20164</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>64311</t>
+          <t>65960</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97679</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51155</t>
+          <t>51152</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77439</t>
+          <t>77418</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66105</t>
+          <t>66201</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>85246</t>
+          <t>85287</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>123349</t>
+          <t>123963</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>158842</t>
+          <t>158504</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,6%</t>
         </is>
       </c>
     </row>
@@ -7908,12 +7908,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39454</t>
+          <t>38665</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64173</t>
+          <t>64580</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7923,12 +7923,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7943,12 +7943,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14316</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31965</t>
+          <t>33949</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7978,12 +7978,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>58090</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91240</t>
+          <t>90536</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8021,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30740</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8036,12 +8036,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>12507</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17085</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38125</t>
+          <t>37527</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -8134,12 +8134,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19295</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>40337</t>
+          <t>39844</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>19761</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>40184</t>
+          <t>42490</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -8219,12 +8219,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>860</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -8379,7 +8379,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8552,7 +8552,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>5736</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>62,08%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>508040</t>
+          <t>506868</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>581427</t>
+          <t>585366</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>690314</t>
+          <t>689611</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>748661</t>
+          <t>751952</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1216608</t>
+          <t>1213629</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1316116</t>
+          <t>1316703</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -9615,12 +9615,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>328787</t>
+          <t>330127</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>395988</t>
+          <t>398178</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9630,12 +9630,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>168542</t>
+          <t>170059</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>219340</t>
+          <t>218211</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>516810</t>
+          <t>509085</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>599167</t>
+          <t>595963</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9700,12 +9700,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,35%</t>
         </is>
       </c>
     </row>
@@ -9728,12 +9728,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>201614</t>
+          <t>199717</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>259652</t>
+          <t>261724</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>49049</t>
+          <t>49021</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>79149</t>
+          <t>80186</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9778,12 +9778,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>260269</t>
+          <t>258213</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>324340</t>
+          <t>325542</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -9813,12 +9813,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,3%</t>
         </is>
       </c>
     </row>
@@ -9841,12 +9841,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>248389</t>
+          <t>243643</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>308930</t>
+          <t>304874</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -9856,12 +9856,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -9876,12 +9876,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>45228</t>
+          <t>44228</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>75326</t>
+          <t>74571</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>302411</t>
+          <t>303733</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>369739</t>
+          <t>373183</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -9926,12 +9926,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -10301,32 +10301,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19943</t>
+          <t>16324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10336,32 +10336,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26839</t>
+          <t>32116</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18682</t>
+          <t>23498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32948</t>
+          <t>39137</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10371,32 +10371,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35174</t>
+          <t>38576</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22055</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47174</t>
+          <t>52112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>54,7%</t>
         </is>
       </c>
     </row>
@@ -10414,32 +10414,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11317</t>
+          <t>14188</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4516</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23287</t>
+          <t>27311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10449,32 +10449,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5618</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10484,32 +10484,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>16935</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8304</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30327</t>
+          <t>36157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -10527,32 +10527,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>12026</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18321</t>
+          <t>23658</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10562,7 +10562,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>11486</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10597,32 +10597,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11417</t>
+          <t>15076</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21893</t>
+          <t>29362</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -10640,32 +10640,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11567</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24113</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10675,32 +10675,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10710,32 +10710,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16547</t>
+          <t>20560</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>10756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32075</t>
+          <t>35394</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -10753,17 +10753,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40031</t>
+          <t>47889</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40031</t>
+          <t>47889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40031</t>
+          <t>47889</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10788,17 +10788,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>47375</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>47375</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>47375</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10823,17 +10823,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>80072</t>
+          <t>95264</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80072</t>
+          <t>95264</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80072</t>
+          <t>95264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10870,32 +10870,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>72975</t>
+          <t>81783</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57199</t>
+          <t>63944</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91432</t>
+          <t>99678</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,19%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10905,32 +10905,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>107625</t>
+          <t>118590</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>96665</t>
+          <t>106171</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117432</t>
+          <t>129121</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10940,32 +10940,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>180600</t>
+          <t>200373</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>160133</t>
+          <t>177507</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>200574</t>
+          <t>224825</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>49,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,76%</t>
         </is>
       </c>
     </row>
@@ -10983,32 +10983,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33831</t>
+          <t>36008</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20669</t>
+          <t>23568</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47400</t>
+          <t>50907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11018,32 +11018,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14877</t>
+          <t>17169</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32618</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11053,32 +11053,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>57102</t>
+          <t>62626</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41944</t>
+          <t>47466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74298</t>
+          <t>80188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,38%</t>
         </is>
       </c>
     </row>
@@ -11096,32 +11096,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34010</t>
+          <t>36690</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>22968</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50861</t>
+          <t>52733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11131,32 +11131,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>13084</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11166,32 +11166,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>39805</t>
+          <t>42983</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25737</t>
+          <t>29089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57366</t>
+          <t>60120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -11209,32 +11209,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>34125</t>
+          <t>44057</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22036</t>
+          <t>30523</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48747</t>
+          <t>61610</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11244,32 +11244,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5905</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12751</t>
+          <t>15381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11279,32 +11279,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40030</t>
+          <t>52271</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26595</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>55521</t>
+          <t>72989</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -11322,17 +11322,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>174941</t>
+          <t>198539</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>174941</t>
+          <t>198539</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>174941</t>
+          <t>198539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11357,17 +11357,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>142596</t>
+          <t>159716</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142596</t>
+          <t>159716</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>142596</t>
+          <t>159716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11392,17 +11392,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>317537</t>
+          <t>358254</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>317537</t>
+          <t>358254</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>317537</t>
+          <t>358254</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11439,32 +11439,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>105295</t>
+          <t>119168</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89724</t>
+          <t>102456</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120179</t>
+          <t>138350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11474,32 +11474,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>103362</t>
+          <t>116900</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93496</t>
+          <t>106464</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113175</t>
+          <t>128251</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11509,32 +11509,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>208658</t>
+          <t>236069</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>189469</t>
+          <t>211804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228470</t>
+          <t>254929</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -11552,32 +11552,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58805</t>
+          <t>67198</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43947</t>
+          <t>52094</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>72533</t>
+          <t>81867</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11587,32 +11587,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>28956</t>
+          <t>31285</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21527</t>
+          <t>23246</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37758</t>
+          <t>40357</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11622,32 +11622,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>87761</t>
+          <t>98483</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>73139</t>
+          <t>83026</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>104379</t>
+          <t>118238</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -11665,32 +11665,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>30944</t>
+          <t>36184</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21900</t>
+          <t>25328</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43070</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11700,32 +11700,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19026</t>
+          <t>20876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11735,32 +11735,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>42682</t>
+          <t>49874</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31829</t>
+          <t>38015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>55390</t>
+          <t>65548</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -11778,32 +11778,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40119</t>
+          <t>52594</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29614</t>
+          <t>39432</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54623</t>
+          <t>68662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11813,32 +11813,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>16895</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>24642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11848,32 +11848,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>54190</t>
+          <t>69490</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42771</t>
+          <t>56239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69302</t>
+          <t>86361</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>19,03%</t>
         </is>
       </c>
     </row>
@@ -11891,17 +11891,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>235164</t>
+          <t>275144</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>235164</t>
+          <t>275144</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>235164</t>
+          <t>275144</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11926,17 +11926,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>158127</t>
+          <t>178771</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158127</t>
+          <t>178771</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>158127</t>
+          <t>178771</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11961,17 +11961,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>393291</t>
+          <t>453915</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>393291</t>
+          <t>453915</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>393291</t>
+          <t>453915</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12008,32 +12008,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>105290</t>
+          <t>112242</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31813</t>
+          <t>95066</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>215164</t>
+          <t>128951</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12043,32 +12043,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>156338</t>
+          <t>166332</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94298</t>
+          <t>156644</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>185055</t>
+          <t>176285</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12078,32 +12078,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>261629</t>
+          <t>278573</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106228</t>
+          <t>258338</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>408012</t>
+          <t>301854</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -12121,32 +12121,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>74580</t>
+          <t>79498</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>64967</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>155802</t>
+          <t>96253</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12156,32 +12156,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>63515</t>
+          <t>34622</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32087</t>
+          <t>26314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>134629</t>
+          <t>43228</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12191,32 +12191,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>138095</t>
+          <t>114121</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53645</t>
+          <t>95836</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>239078</t>
+          <t>131726</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -12234,32 +12234,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>35314</t>
+          <t>41721</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>30345</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75914</t>
+          <t>54589</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12269,32 +12269,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>14262</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12304,32 +12304,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>43629</t>
+          <t>51291</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>16165</t>
+          <t>38556</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71241</t>
+          <t>66207</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -12347,32 +12347,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>287758</t>
+          <t>52653</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76775</t>
+          <t>40610</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>440439</t>
+          <t>68528</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12382,32 +12382,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18991</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12417,32 +12417,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>300087</t>
+          <t>66117</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74829</t>
+          <t>51847</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>571290</t>
+          <t>82376</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -12460,17 +12460,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>502942</t>
+          <t>286114</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>502942</t>
+          <t>286114</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>502942</t>
+          <t>286114</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12495,17 +12495,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>240497</t>
+          <t>223988</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>240497</t>
+          <t>223988</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>240497</t>
+          <t>223988</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12530,17 +12530,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>743440</t>
+          <t>510102</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>743440</t>
+          <t>510102</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>743440</t>
+          <t>510102</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12577,32 +12577,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>67567</t>
+          <t>71404</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56393</t>
+          <t>60044</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>79698</t>
+          <t>83311</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12612,32 +12612,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>64488</t>
+          <t>73279</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>57800</t>
+          <t>65628</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>70542</t>
+          <t>79766</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12647,32 +12647,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>132055</t>
+          <t>144683</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>118570</t>
+          <t>129412</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>146188</t>
+          <t>158256</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,22%</t>
         </is>
       </c>
     </row>
@@ -12690,32 +12690,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>31333</t>
+          <t>33253</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22420</t>
+          <t>24447</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42267</t>
+          <t>44645</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12725,32 +12725,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>16465</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19732</t>
+          <t>23125</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12760,27 +12760,27 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>45755</t>
+          <t>49718</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35063</t>
+          <t>39412</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56862</t>
+          <t>61767</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -12803,32 +12803,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>23297</t>
+          <t>24144</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15831</t>
+          <t>16292</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33244</t>
+          <t>33982</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12838,32 +12838,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9612</t>
+          <t>10021</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12873,32 +12873,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>28531</t>
+          <t>29682</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>19962</t>
+          <t>20978</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39521</t>
+          <t>40711</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -12916,32 +12916,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>29713</t>
+          <t>32532</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>39349</t>
+          <t>43455</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12951,32 +12951,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5891</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12986,32 +12986,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>38723</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>26681</t>
+          <t>30057</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>47281</t>
+          <t>50455</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -13029,17 +13029,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>151910</t>
+          <t>161333</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>151910</t>
+          <t>161333</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>151910</t>
+          <t>161333</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13064,17 +13064,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>90035</t>
+          <t>101473</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>90035</t>
+          <t>101473</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>90035</t>
+          <t>101473</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13099,17 +13099,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>241945</t>
+          <t>262806</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>241945</t>
+          <t>262806</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>241945</t>
+          <t>262806</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13146,27 +13146,27 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5584</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3122</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -13181,27 +13181,27 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7500</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5853</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -13216,32 +13216,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9974</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14496</t>
+          <t>15819</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -13304,12 +13304,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13329,7 +13329,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -13339,12 +13339,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>3609</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -13354,7 +13354,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -13372,7 +13372,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -13382,12 +13382,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -13397,7 +13397,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13442,7 +13442,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>655</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -13452,12 +13452,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2954</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>816</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -13510,7 +13510,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>816</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -13598,17 +13598,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -13633,17 +13633,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>8648</t>
+          <t>9055</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -13668,17 +13668,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -14167,17 +14167,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14237,17 +14237,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14284,32 +14284,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>366644</t>
+          <t>398826</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>208745</t>
+          <t>365424</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>483375</t>
+          <t>434101</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -14319,32 +14319,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>466154</t>
+          <t>515112</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>365120</t>
+          <t>494051</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>498252</t>
+          <t>536914</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -14354,32 +14354,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>832798</t>
+          <t>913937</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>552664</t>
+          <t>871720</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>990896</t>
+          <t>954335</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>56,18%</t>
         </is>
       </c>
     </row>
@@ -14397,32 +14397,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>209866</t>
+          <t>230145</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>113770</t>
+          <t>202082</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>279671</t>
+          <t>261093</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14432,32 +14432,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>136929</t>
+          <t>117014</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>101706</t>
+          <t>99516</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>245332</t>
+          <t>134205</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14467,32 +14467,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>346795</t>
+          <t>347159</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>224103</t>
+          <t>314004</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>439479</t>
+          <t>383578</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -14510,32 +14510,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>133041</t>
+          <t>151420</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>73875</t>
+          <t>127968</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>179885</t>
+          <t>176395</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14545,32 +14545,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>33687</t>
+          <t>38140</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>28548</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>45277</t>
+          <t>50862</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -14580,32 +14580,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>166728</t>
+          <t>189560</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>105177</t>
+          <t>161946</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>209816</t>
+          <t>220357</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -14623,32 +14623,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>403446</t>
+          <t>197866</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>193105</t>
+          <t>169159</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>695128</t>
+          <t>229166</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -14658,32 +14658,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>43174</t>
+          <t>50112</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>33124</t>
+          <t>37828</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>55349</t>
+          <t>62793</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -14693,32 +14693,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>446619</t>
+          <t>247978</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>221107</t>
+          <t>218257</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>918309</t>
+          <t>282131</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -14736,17 +14736,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1112997</t>
+          <t>978257</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -14771,17 +14771,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>679944</t>
+          <t>720378</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -14806,17 +14806,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1792941</t>
+          <t>1698635</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
